--- a/USE_THIS_DESIGN_CODE/Input Excel Sheets/Design Configurations/ASEN4138_TestCases.xlsx
+++ b/USE_THIS_DESIGN_CODE/Input Excel Sheets/Design Configurations/ASEN4138_TestCases.xlsx
@@ -1906,7 +1906,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D116"/>
+  <dimension ref="A1:D121"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.1640625" customWidth="1"/>
@@ -3521,6 +3521,116 @@
       </c>
       <c r="D116" t="s">
         <v>210</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Component_Data</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>SkinThick_w</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>ft</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Hollow skin wall thickness. Blank uses Thick_f from the same component row. Weight = density * wetted area * wall thickness * 1.05; internal structure is not included.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Component_Data</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>SkinThick_h1</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>ft</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Hollow skin wall thickness. Blank uses Thick_f from the same component row. Weight = density * wetted area * wall thickness * 1.05; internal structure is not included.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Component_Data</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>SkinThick_h2</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>ft</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Hollow skin wall thickness. Blank uses Thick_f from the same component row. Weight = density * wetted area * wall thickness * 1.05; internal structure is not included.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Component_Data</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>SkinThick_v1</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>ft</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Hollow skin wall thickness. Blank uses Thick_f from the same component row. Weight = density * wetted area * wall thickness * 1.05; internal structure is not included.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Component_Data</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>SkinThick_v2</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>ft</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Hollow skin wall thickness. Blank uses Thick_f from the same component row. Weight = density * wetted area * wall thickness * 1.05; internal structure is not included.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -6347,10 +6457,11 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:AI8"/>
+  <dimension ref="A1:AN8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="35" width="18" customWidth="1"/>
+    <col min="36" max="40" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6459,6 +6570,31 @@
       <c r="AI1" t="s">
         <v>209</v>
       </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>SkinThick_w</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>SkinThick_h1</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>SkinThick_h2</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>SkinThick_v1</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>SkinThick_v2</t>
+        </is>
+      </c>
     </row>
     <row r="2" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
